--- a/data/trans_dic/IP16B02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16B02-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre (tasa de respuesta: 98,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,98; 100,0</t>
+          <t>53,45; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,13; 92,96</t>
+          <t>46,22; 92,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,71; 88,11</t>
+          <t>23,07; 82,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55,98; 100,0</t>
+          <t>56,61; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,21; 100,0</t>
+          <t>53,35; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,87; 96,0</t>
+          <t>66,66; 96,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,14; 92,05</t>
+          <t>61,29; 92,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,27; 93,59</t>
+          <t>51,73; 93,57</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,88; 89,66</t>
+          <t>62,48; 89,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,87; 86,61</t>
+          <t>67,28; 86,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,37; 95,17</t>
+          <t>79,05; 95,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,4; 96,38</t>
+          <t>77,42; 96,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,01; 94,99</t>
+          <t>80,59; 95,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,73; 95,97</t>
+          <t>75,99; 95,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,48; 91,36</t>
+          <t>76,13; 91,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,06; 89,07</t>
+          <t>77,39; 88,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,3; 94,39</t>
+          <t>82,15; 94,23</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45,86; 100,0</t>
+          <t>51,98; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,29; 100,0</t>
+          <t>76,69; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,88; 91,58</t>
+          <t>59,48; 91,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69,66; 96,25</t>
+          <t>71,92; 96,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,87; 95,37</t>
+          <t>60,08; 95,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,62; 100,0</t>
+          <t>73,76; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,41; 94,49</t>
+          <t>70,14; 95,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74,67; 95,78</t>
+          <t>75,37; 96,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74,74; 94,31</t>
+          <t>72,43; 94,03</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,76; 88,59</t>
+          <t>67,27; 88,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,45; 87,43</t>
+          <t>72,48; 87,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,84; 90,06</t>
+          <t>73,71; 90,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,81; 94,57</t>
+          <t>81,24; 94,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,6; 92,79</t>
+          <t>79,87; 93,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,35; 96,15</t>
+          <t>83,34; 95,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,67; 90,1</t>
+          <t>78,36; 90,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>77,77; 88,87</t>
+          <t>79,11; 88,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>81,04; 91,57</t>
+          <t>80,82; 91,34</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre (tasa de respuesta: 98,35%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5752</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7446</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7979</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6778</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13731</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>14224</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9453</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3718; 6955</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4523; 9086</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1546; 5505</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5286; 9338</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4347; 8147</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>10860; 15676</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>10991; 16640</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6347; 11481</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>20815</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40395</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34848</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28205</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>46684</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26805</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>49020</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>87079</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>61653</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>16466; 23641</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>34845; 44640</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>30868; 37452</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>24272; 30141</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>42142; 49687</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22885; 28892</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>43927; 52572</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>80554; 92504</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>56813; 65170</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6054</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15840</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12878</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15237</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14666</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>21291</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>27617</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>27543</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3794; 7299</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13138; 17132</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9649; 14895</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12449; 16659</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8490; 13488</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>11802; 16000</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17262; 23400</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>23564; 30016</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>23339; 30301</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>32622</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>63680</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>51613</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51421</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>65240</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47036</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84043</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>128920</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>98649</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>27316; 36076</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>57051; 68588</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>45684; 55848</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>47118; 54675</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>59559; 69537</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>43068; 49505</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>77266; 88783</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>121270; 136264</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>91854; 103806</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16B02-Estudios-trans_dic.xlsx
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,45; 100,0</t>
+          <t>44,79; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,22; 92,85</t>
+          <t>47,18; 93,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,07; 82,12</t>
+          <t>26,24; 88,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,61; 100,0</t>
+          <t>56,3; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,35; 100,0</t>
+          <t>49,59; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,66; 96,21</t>
+          <t>64,3; 95,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,29; 92,79</t>
+          <t>58,84; 91,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51,73; 93,57</t>
+          <t>52,6; 93,56</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,48; 89,71</t>
+          <t>63,02; 90,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,28; 86,19</t>
+          <t>67,47; 86,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,05; 95,92</t>
+          <t>78,41; 95,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,42; 96,15</t>
+          <t>78,7; 96,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,59; 95,01</t>
+          <t>80,43; 94,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,99; 95,94</t>
+          <t>76,68; 95,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,13; 91,11</t>
+          <t>75,63; 91,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,39; 88,87</t>
+          <t>77,18; 88,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,15; 94,23</t>
+          <t>81,73; 93,89</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,98; 100,0</t>
+          <t>51,09; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,69; 100,0</t>
+          <t>77,73; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,48; 91,82</t>
+          <t>58,46; 92,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,92; 96,23</t>
+          <t>70,24; 96,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,08; 95,45</t>
+          <t>58,53; 95,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,76; 100,0</t>
+          <t>73,78; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,14; 95,08</t>
+          <t>73,75; 95,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75,37; 96,01</t>
+          <t>75,36; 95,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72,43; 94,03</t>
+          <t>74,01; 94,17</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,27; 88,84</t>
+          <t>68,48; 88,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,48; 87,14</t>
+          <t>72,72; 87,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,71; 90,11</t>
+          <t>74,2; 89,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81,24; 94,27</t>
+          <t>80,72; 94,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,87; 93,25</t>
+          <t>79,63; 93,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,34; 95,79</t>
+          <t>82,2; 96,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,36; 90,04</t>
+          <t>79,01; 90,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,11; 88,9</t>
+          <t>78,87; 88,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>80,82; 91,34</t>
+          <t>80,87; 91,38</t>
         </is>
       </c>
     </row>
@@ -1306,27 +1306,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3718; 6955</t>
+          <t>3115; 6955</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4523; 9086</t>
+          <t>4617; 9109</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1546; 5505</t>
+          <t>1759; 5930</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5286; 9338</t>
+          <t>5258; 9338</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4347; 8147</t>
+          <t>4040; 8147</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10860; 15676</t>
+          <t>10477; 15635</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10991; 16640</t>
+          <t>10552; 16474</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6347; 11481</t>
+          <t>6454; 11480</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16466; 23641</t>
+          <t>16607; 23731</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34845; 44640</t>
+          <t>34943; 45035</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30868; 37452</t>
+          <t>30616; 37160</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24272; 30141</t>
+          <t>24673; 30193</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42142; 49687</t>
+          <t>42059; 49666</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22885; 28892</t>
+          <t>23091; 28895</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43927; 52572</t>
+          <t>43639; 52668</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80554; 92504</t>
+          <t>80339; 92271</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56813; 65170</t>
+          <t>56526; 64934</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3794; 7299</t>
+          <t>3729; 7299</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13138; 17132</t>
+          <t>13317; 17132</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9649; 14895</t>
+          <t>9484; 15006</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12449; 16659</t>
+          <t>12160; 16650</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8490; 13488</t>
+          <t>8271; 13479</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11802; 16000</t>
+          <t>11805; 16000</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17262; 23400</t>
+          <t>18150; 23451</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23564; 30016</t>
+          <t>23562; 29969</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23339; 30301</t>
+          <t>23848; 30346</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27316; 36076</t>
+          <t>27806; 36010</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57051; 68588</t>
+          <t>57235; 68961</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45684; 55848</t>
+          <t>45988; 55696</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47118; 54675</t>
+          <t>46813; 54589</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59559; 69537</t>
+          <t>59379; 69492</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43068; 49505</t>
+          <t>42480; 49702</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77266; 88783</t>
+          <t>77913; 89306</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>121270; 136264</t>
+          <t>120894; 135732</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91854; 103806</t>
+          <t>91907; 103862</t>
         </is>
       </c>
     </row>
